--- a/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N59_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7486_W0023F0001T0006Z000C1N59_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>82.95017013777519</v>
+        <v>13.47940264738847</v>
       </c>
       <c r="D2" t="n">
-        <v>88.28450763614731</v>
+        <v>14.34623249087394</v>
       </c>
       <c r="E2" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F2" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>70.82640715298372</v>
+        <v>11.50929116235985</v>
       </c>
       <c r="D3" t="n">
-        <v>75.94799751177577</v>
+        <v>12.34154959566356</v>
       </c>
       <c r="E3" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F3" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>80.99163149415735</v>
+        <v>13.16114011780057</v>
       </c>
       <c r="D4" t="n">
-        <v>86.28680704729409</v>
+        <v>14.02160614518529</v>
       </c>
       <c r="E4" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F4" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.40225395838269</v>
+        <v>10.14036626823719</v>
       </c>
       <c r="D5" t="n">
-        <v>67.67435836964232</v>
+        <v>10.99708323506688</v>
       </c>
       <c r="E5" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F5" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.84695413712476</v>
+        <v>9.075130047282775</v>
       </c>
       <c r="D6" t="n">
-        <v>60.37068940728033</v>
+        <v>9.810237028683055</v>
       </c>
       <c r="E6" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F6" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.60966455259165</v>
+        <v>11.47407048979614</v>
       </c>
       <c r="D7" t="n">
-        <v>75.6191268364788</v>
+        <v>12.2881081109278</v>
       </c>
       <c r="E7" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F7" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>58.26335893916182</v>
+        <v>9.467795827613795</v>
       </c>
       <c r="D8" t="n">
-        <v>62.89899569886334</v>
+        <v>10.22108680106529</v>
       </c>
       <c r="E8" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F8" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.49551849626927</v>
+        <v>3.493021755643756</v>
       </c>
       <c r="D9" t="n">
-        <v>26.05569479249507</v>
+        <v>4.234050403780449</v>
       </c>
       <c r="E9" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F9" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.5879015958523</v>
+        <v>2.695534009325999</v>
       </c>
       <c r="D10" t="n">
-        <v>18.29579328555999</v>
+        <v>2.973066408903498</v>
       </c>
       <c r="E10" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F10" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>44.7980301760796</v>
+        <v>7.279679903612935</v>
       </c>
       <c r="D11" t="n">
-        <v>43.27550632029136</v>
+        <v>7.032269777047346</v>
       </c>
       <c r="E11" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F11" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.15056464246525</v>
+        <v>6.361966754400603</v>
       </c>
       <c r="D12" t="n">
-        <v>41.62295638280473</v>
+        <v>6.763730412205769</v>
       </c>
       <c r="E12" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F12" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.25192155248696</v>
+        <v>5.728437252279131</v>
       </c>
       <c r="D13" t="n">
-        <v>36.7023872760944</v>
+        <v>5.96413793236534</v>
       </c>
       <c r="E13" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F13" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>40.30978901762728</v>
+        <v>6.550340715364434</v>
       </c>
       <c r="D14" t="n">
-        <v>40.79692115697658</v>
+        <v>6.629499688008694</v>
       </c>
       <c r="E14" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F14" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>35.52870225183927</v>
+        <v>5.773414115923882</v>
       </c>
       <c r="D15" t="n">
-        <v>35.38474321323383</v>
+        <v>5.750020772150498</v>
       </c>
       <c r="E15" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F15" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>25.29044224474433</v>
+        <v>4.109696864770954</v>
       </c>
       <c r="D16" t="n">
-        <v>19.95952634219806</v>
+        <v>3.243423030607186</v>
       </c>
       <c r="E16" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F16" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>39.20547749527239</v>
+        <v>6.370890092981764</v>
       </c>
       <c r="D17" t="n">
-        <v>34.59785043070727</v>
+        <v>5.622150694989931</v>
       </c>
       <c r="E17" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F17" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>29.44967804567221</v>
+        <v>4.785572682421734</v>
       </c>
       <c r="D18" t="n">
-        <v>25.25857765675402</v>
+        <v>4.104518869222528</v>
       </c>
       <c r="E18" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F18" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>38.70200068641402</v>
+        <v>6.289075111542278</v>
       </c>
       <c r="D19" t="n">
-        <v>33.36766724589091</v>
+        <v>5.422245927457274</v>
       </c>
       <c r="E19" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F19" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>38.31258922542683</v>
+        <v>6.22579574913186</v>
       </c>
       <c r="D20" t="n">
-        <v>34.97845923698495</v>
+        <v>5.683999626010055</v>
       </c>
       <c r="E20" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F20" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>47.82268890697409</v>
+        <v>7.771186947383289</v>
       </c>
       <c r="D21" t="n">
-        <v>44.56073285632989</v>
+        <v>7.241119089153607</v>
       </c>
       <c r="E21" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F21" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>46.34444080297919</v>
+        <v>7.530971630484118</v>
       </c>
       <c r="D22" t="n">
-        <v>41.68780845444052</v>
+        <v>6.774268873846585</v>
       </c>
       <c r="E22" t="n">
-        <v>18.19836656418801</v>
+        <v>2.957234566680552</v>
       </c>
       <c r="F22" t="n">
-        <v>20.78097375071219</v>
+        <v>3.376908234490732</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
